--- a/medical_surveys_questionnaires/041_post_vaccination_questionnaire--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/041_post_vaccination_questionnaire--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1594,46 +1594,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>motrin</t>
+          <t>excedrin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Motrin</t>
+          <t>Excedrin</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>excedrin</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Excedrin</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>excedrin</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Excedrin</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>asthma</t>
+          <t>kidney_disease</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Asthma</t>
+          <t>Kidney disease</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>hypertension</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Heart disease</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kidney_disease</t>
+          <t>stroke</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kidney disease</t>
+          <t>Stroke</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>heart_disease</t>
+          <t>thyroid_disease</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Heart disease</t>
+          <t>Thyroid disease</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>stroke</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stroke</t>
+          <t>Cancer</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>thyroid_disease</t>
+          <t>pulmonary_disease</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thyroid disease</t>
+          <t>Pulmonary disease</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>chronic_bronchitis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cancer</t>
+          <t>Chronic bronchitis</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pulmonary_disease</t>
+          <t>chronic_asthma</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pulmonary disease</t>
+          <t>Chronic asthma</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>chronic_bronchitis</t>
+          <t>chronic_obstructive_pulmonary_disease</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chronic bronchitis</t>
+          <t>Chronic obstructive pulmonary disease</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>chronic_asthma</t>
+          <t>chronic_kidney_disease</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chronic asthma</t>
+          <t>Chronic kidney disease</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>chronic_bronchitis</t>
+          <t>chronic_liver_disease</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chronic bronchitis</t>
+          <t>Chronic liver disease</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>chronic_obstructive_pulmonary_disease</t>
+          <t>liver_disease</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chronic obstructive pulmonary disease</t>
+          <t>Liver disease</t>
         </is>
       </c>
     </row>
@@ -1866,114 +1866,114 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>chronic_kidney_disease</t>
+          <t>gastrointestinal_disorder</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chronic kidney disease</t>
+          <t>Gastrointestinal disorder</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>patient_gender_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>chronic_liver_disease</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chronic liver disease</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>patient_gender_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>liver_disease</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Liver disease</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>medical_condition_choices</t>
+          <t>patient_gender_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gastrointestinal_disorder</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gastrointestinal disorder</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>patient_gender_choices</t>
+          <t>medical_license_number_state_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>patient_gender_choices</t>
+          <t>medical_license_number_state_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>patient_gender_choices</t>
+          <t>medical_license_number_state_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>alabama</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>alaska</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>arizona</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>arkansas</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>california</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>colorado</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>connecticut</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>delaware</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>district_of_columbia</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>florida</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>georgia</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hawaii</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>idaho</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>illinois</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>indiana</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>iowa</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kansas</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kentucky</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>louisiana</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>maine</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>maryland</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>massachusetts</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2359,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>michigan</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>minnesota</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>mississippi</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>missouri</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nebraska</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nevada</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>new_hampshire</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>new_jersey</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2495,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>new_mexico</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>north_carolina</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>north_dakota</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ohio</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>oklahoma</t>
+          <t>puerto_rico</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>oregon</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>pennsylvania</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2631,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>puerto_rico</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>rhode_island</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>south_carolina</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>south_dakota</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>tennessee</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2716,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>texas</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>utah</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>vermont</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>virginia</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2784,61 +2784,10 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>washington</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>medical_license_number_state_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>west_virginia</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>medical_license_number_state_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>wisconsin</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>medical_license_number_state_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>wyoming</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
         <is>
           <t>Wyoming</t>
         </is>
